--- a/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,314 +656,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>186900</v>
+      </c>
+      <c r="E8" s="3">
         <v>150100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>152500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>130200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>175400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>145800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>137800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>118100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>161300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>131900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>114500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>60700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>82000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>61000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>42300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>36300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>48500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>41400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E9" s="3">
         <v>84900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>130200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>124800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>111000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>71800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>65000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>59400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>66800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>63500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>50500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>21000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13900</v>
-      </c>
-      <c r="U9" s="3">
-        <v>15100</v>
       </c>
       <c r="V9" s="3">
         <v>15100</v>
       </c>
       <c r="W9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="X9" s="3">
         <v>15500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>116900</v>
+      </c>
+      <c r="E10" s="3">
         <v>65200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>64400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>74000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>72800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>58700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>94500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>68400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>64000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>39900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>60800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>40000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>20800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>35200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>17300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>25900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,76 +1000,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E12" s="3">
         <v>23300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>22800</v>
       </c>
       <c r="J12" s="3">
         <v>22800</v>
       </c>
       <c r="K12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="L12" s="3">
         <v>20800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,59 +1140,62 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-5400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1200</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>32000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11300</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1192,8 +1211,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1201,67 +1223,70 @@
         <v>2900</v>
       </c>
       <c r="E15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F15" s="3">
         <v>7600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>15400</v>
       </c>
       <c r="G15" s="3">
         <v>15400</v>
       </c>
       <c r="H15" s="3">
+        <v>15400</v>
+      </c>
+      <c r="I15" s="3">
         <v>19200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>23800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>23900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4700</v>
-      </c>
-      <c r="R15" s="3">
-        <v>500</v>
       </c>
       <c r="S15" s="3">
         <v>500</v>
       </c>
       <c r="T15" s="3">
+        <v>500</v>
+      </c>
+      <c r="U15" s="3">
         <v>300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>600</v>
-      </c>
-      <c r="W15" s="3">
-        <v>500</v>
       </c>
       <c r="X15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>143500</v>
+      </c>
+      <c r="E17" s="3">
         <v>163800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>218900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>222100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>203900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>167000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>161000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>157900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>157700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>155800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>161500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>74500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>74000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>71900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>82900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>47000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>44300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>46500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>45700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-66400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-91900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-28500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-21200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-23200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-39800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-47000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-40600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-10700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,144 +1477,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E21" s="3">
         <v>20800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>38300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>21800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>21100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>47400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>19100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-24300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1900</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
         <v>-4600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,144 +1688,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-73200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-99000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-39100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-46600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-29000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-50900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-38800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-87700</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
       <c r="P24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-900</v>
-      </c>
-      <c r="T24" s="3">
-        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>100</v>
       </c>
       <c r="V24" s="3">
+        <v>100</v>
+      </c>
+      <c r="W24" s="3">
         <v>-700</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-73900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-98700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-36400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-44600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-39100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-73900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-98700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-36400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-44600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-39100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2113,20 +2173,23 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>10</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2327,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E32" s="3">
         <v>4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-73900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-98700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-36400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-44600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-39100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-73900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-98700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-36400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-44600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-39100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2743,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>326200</v>
+      </c>
+      <c r="E41" s="3">
         <v>310500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>266400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>236600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>326300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>253600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>233100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>204600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>230400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>188200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>193000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>468600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>117700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>103800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>107500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>71300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>88900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>85100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>86100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>80700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>80500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>82400</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2789,81 +2878,87 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>7500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1176300</v>
+      </c>
+      <c r="E43" s="3">
         <v>937200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>908400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>875300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>976500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>804400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>886100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>783000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>927800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>765100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>780500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>401800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>471700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>412400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>292400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>158200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>217600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>172300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>178000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>155900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>205700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>155300</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,144 +3025,153 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E45" s="3">
         <v>21500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1523000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1269200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1196900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1137000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1326300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1079300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1141800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1009800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1178100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>974300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1004000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>887800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>607100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>529600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>410200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>236900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>313100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>263200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>270000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>244100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>300500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>260900</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3134,144 +3238,153 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E48" s="3">
         <v>110700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>115300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>116800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>123200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>119900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>112100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>107300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>111100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>97400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>83400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>66200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>63300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>61600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>63500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>41100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>45200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>47000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>38800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>41100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>33500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1051200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1058500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1088500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1168500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1255400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1323800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1361400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1398500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1416600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1455400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1447000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>256500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>264200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>272300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>280000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>34300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>34800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>24200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>24700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3522,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3415,49 +3534,49 @@
         <v>6700</v>
       </c>
       <c r="E52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F52" s="3">
         <v>7000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>6900</v>
       </c>
       <c r="K52" s="3">
         <v>6900</v>
       </c>
       <c r="L52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="M52" s="3">
         <v>6100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1900</v>
-      </c>
-      <c r="S52" s="3">
-        <v>2100</v>
       </c>
       <c r="T52" s="3">
         <v>2100</v>
@@ -3469,13 +3588,16 @@
         <v>2100</v>
       </c>
       <c r="W52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="X52" s="3">
         <v>1200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3664,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2688800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2445000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2407800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2429900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2712200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2529100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2622500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2522500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2712600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2533100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2541300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1214700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>939000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>866500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>757100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>314200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>395100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>335300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>334800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>311400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>360000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,76 +3791,80 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1357100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1085700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1006600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>934800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1076900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>872700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>953500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>838700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>983100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>806500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>820100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>426700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>496900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>444400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>337700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>188800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>252700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>207300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>182500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>233500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3765,8 +3898,8 @@
       <c r="M58" s="3">
         <v>3600</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>10</v>
+      <c r="N58" s="3">
+        <v>3600</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>10</v>
@@ -3783,8 +3916,8 @@
       <c r="S58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3798,183 +3931,192 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E59" s="3">
         <v>41700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>43900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>44000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>42700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>45100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>42700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>48800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>50000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>29200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1402100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1131100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1054000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>982400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1125000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>919000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1002200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>887300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1029400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>858900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>873700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>449000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>522200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>473600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>362300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>202100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>267500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>214500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>220500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>195500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>241000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>202200</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>533000</v>
+      </c>
+      <c r="E61" s="3">
         <v>601600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>635000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>674000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>722800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>722100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>721400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>720700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>720000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>719300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>718600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>388600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4002,76 +4144,82 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E62" s="3">
         <v>60200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>66100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>68300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>73100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>77500</v>
       </c>
       <c r="I62" s="3">
         <v>77500</v>
       </c>
       <c r="J62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="K62" s="3">
         <v>76500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>82400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>78100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>61300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>34800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>35100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>36700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>37300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4428,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1987100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1792900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1755200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1724600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1920900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1718600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1801100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1684600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1831900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1656300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1653600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>872400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>557300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>510300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>399700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>216000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>283200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>231200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>229200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>202900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>242000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4810,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-684000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-714900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-697400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-623500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-524800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-488400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-464000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-439000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-394500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-394900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-370600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-407400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-394500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-400400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-389900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-350800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-341100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-342600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-336400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-328200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-315600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-313400</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5094,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>701700</v>
+      </c>
+      <c r="E76" s="3">
         <v>652100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>652600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>705200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>791300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>810500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>821400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>837900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>880800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>876800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>887700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>342400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>381600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>356100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>357500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>98200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>111900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>104100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>105600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>108500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>118000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-73900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-98700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-36400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-44600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-39100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5412,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E83" s="3">
         <v>39300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>88900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>95800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>77400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>45900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>49800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>48700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>35900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>89100</v>
+      </c>
+      <c r="E89" s="3">
         <v>82100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>74100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>88700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>39900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>42300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>21600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>68600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>30600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-16300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5936,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-636800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>51100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,208 +6529,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-62200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-30600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-33200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-51800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-16400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>332700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>355600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>10600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-800</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E102" s="3">
         <v>44100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-89900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>72700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>28500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>42300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-275400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>350900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>37500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>10100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
@@ -656,326 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>149300</v>
+      </c>
+      <c r="E8" s="3">
         <v>186900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>150100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>152500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>130200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>175400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>145800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>137800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>118100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>161300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>131900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>114500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>60700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>82000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>61000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>42300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>36300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>48500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>37900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>32400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>41400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E9" s="3">
         <v>70000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>84900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>130200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>124800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>111000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>71800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>65000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>59400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>66800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>63500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>50500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>20800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>21200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13900</v>
-      </c>
-      <c r="V9" s="3">
-        <v>15100</v>
       </c>
       <c r="W9" s="3">
         <v>15100</v>
       </c>
       <c r="X9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="Y9" s="3">
         <v>15500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E10" s="3">
         <v>116900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>65200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>64400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>74000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>72800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>58700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>94500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>68400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>64000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>39900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>60800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>40000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>35200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>17300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>25900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E12" s="3">
         <v>23000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24900</v>
-      </c>
-      <c r="J12" s="3">
-        <v>22800</v>
       </c>
       <c r="K12" s="3">
         <v>22800</v>
       </c>
       <c r="L12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="M12" s="3">
         <v>20800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1143,62 +1160,65 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-8300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-5400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1200</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>32000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11300</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1214,8 +1234,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1226,67 +1249,70 @@
         <v>2900</v>
       </c>
       <c r="F15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G15" s="3">
         <v>7600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>15400</v>
       </c>
       <c r="H15" s="3">
         <v>15400</v>
       </c>
       <c r="I15" s="3">
+        <v>15400</v>
+      </c>
+      <c r="J15" s="3">
         <v>19200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>23800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>23900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4700</v>
-      </c>
-      <c r="S15" s="3">
-        <v>500</v>
       </c>
       <c r="T15" s="3">
         <v>500</v>
       </c>
       <c r="U15" s="3">
+        <v>500</v>
+      </c>
+      <c r="V15" s="3">
         <v>300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>600</v>
-      </c>
-      <c r="X15" s="3">
-        <v>500</v>
       </c>
       <c r="Y15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>170500</v>
+      </c>
+      <c r="E17" s="3">
         <v>143500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>163800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>218900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>222100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>203900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>167000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>161000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>157900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>157700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>155800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>161500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>74500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>74000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>71900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>82900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>44300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>46500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>45700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>43900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E18" s="3">
         <v>43400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-66400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-91900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-28500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-21200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-23200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-39800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-47000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-40600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,150 +1511,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E21" s="3">
         <v>50000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>20800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>38300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>21800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>47400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>19100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-24300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1900</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>-4600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1691,150 +1731,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E23" s="3">
         <v>33200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-73200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-99000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-39100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-29000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-50900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-38800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-13300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-87700</v>
-      </c>
-      <c r="O24" s="3">
-        <v>200</v>
       </c>
       <c r="P24" s="3">
         <v>200</v>
       </c>
       <c r="Q24" s="3">
+        <v>200</v>
+      </c>
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-900</v>
-      </c>
-      <c r="U24" s="3">
-        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>100</v>
       </c>
       <c r="W24" s="3">
+        <v>100</v>
+      </c>
+      <c r="X24" s="3">
         <v>-700</v>
-      </c>
-      <c r="X24" s="3">
-        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E26" s="3">
         <v>30900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-73900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-98700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-36400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-24400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-44600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>36800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-39100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-12500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E27" s="3">
         <v>30900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-73900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-98700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-36400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-24400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-44600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>36800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-39100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2176,20 +2237,23 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>10</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E32" s="3">
         <v>10300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E33" s="3">
         <v>30900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-73900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-98700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-36400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-24400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-44600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>36800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-39100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E35" s="3">
         <v>30900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-73900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-98700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-36400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-24400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-44600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>36800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-39100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>252800</v>
+      </c>
+      <c r="E41" s="3">
         <v>326200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>310500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>266400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>236600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>326300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>253600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>233100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>204600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>230400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>188200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>193000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>468600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>117700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>103800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>107500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>71300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>88900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>85100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>86100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>80700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>80500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>82400</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2881,84 +2971,90 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>7500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>999800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1176300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>937200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>908400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>875300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>976500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>804400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>886100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>783000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>927800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>765100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>780500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>401800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>471700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>412400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>292400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>158200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>217600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>172300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>178000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>155900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>205700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>155300</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3028,150 +3124,159 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E45" s="3">
         <v>20500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1273500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1523000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1269200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1196900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1137000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1326300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1079300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1141800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1009800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1178100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>974300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1004000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>887800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>607100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>529600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>410200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>236900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>313100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>263200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>270000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>244100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>260900</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3241,150 +3346,159 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E48" s="3">
         <v>107900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>110700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>115300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>116800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>123200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>119900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>112100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>107300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>111100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>97400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>83400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>66200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>63300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>61600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>63500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>41100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>45200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>47000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>38800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>41100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>33500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1044800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1051200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1058500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1088500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1168500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1255400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1323800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1361400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1398500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1416600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1455400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1447000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>256500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>264200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>272300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>280000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>34300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>34800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>24200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>24700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,61 +3642,64 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6700</v>
+        <v>16300</v>
       </c>
       <c r="E52" s="3">
         <v>6700</v>
       </c>
       <c r="F52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G52" s="3">
         <v>7000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>6900</v>
       </c>
       <c r="L52" s="3">
         <v>6900</v>
       </c>
       <c r="M52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="N52" s="3">
         <v>6100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1900</v>
-      </c>
-      <c r="T52" s="3">
-        <v>2100</v>
       </c>
       <c r="U52" s="3">
         <v>2100</v>
@@ -3591,13 +3711,16 @@
         <v>2100</v>
       </c>
       <c r="X52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2454100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2688800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2445000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2407800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2429900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2712200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2529100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2622500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2522500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2712600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2533100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2541300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1214700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>939000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>866500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>757100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>314200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>395100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>335300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>334800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>311400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>360000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,84 +3922,88 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1105600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1357100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1085700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1006600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>934800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1076900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>872700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>953500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>838700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>983100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>806500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>820100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>426700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>496900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>444400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>337700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>188800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>252700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>200900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>207300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>182500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>233500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="E58" s="3">
         <v>3600</v>
@@ -3901,8 +4035,8 @@
       <c r="N58" s="3">
         <v>3600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>10</v>
+      <c r="O58" s="3">
+        <v>3600</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>10</v>
@@ -3919,8 +4053,8 @@
       <c r="T58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3934,192 +4068,201 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E59" s="3">
         <v>41400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>41700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>43900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>45000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>48800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>50000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>29200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1154700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1402100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1131100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1054000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>982400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1125000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>919000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1002200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>887300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1029400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>858900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>873700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>449000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>522200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>473600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>362300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>202100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>267500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>214500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>220500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>195500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>241000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>202200</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>549100</v>
+      </c>
+      <c r="E61" s="3">
         <v>533000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>601600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>635000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>674000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>722800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>722100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>721400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>720700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>720000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>719300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>718600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>388600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4147,79 +4290,85 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E62" s="3">
         <v>52000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>60200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>66100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>68300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>73100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>77500</v>
       </c>
       <c r="J62" s="3">
         <v>77500</v>
       </c>
       <c r="K62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="L62" s="3">
         <v>76500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>82400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>78100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>61300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>34800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>35100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>36700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>37300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>15700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1758700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1987100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1792900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1755200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1724600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1920900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1718600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1801100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1684600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1831900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1656300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1653600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>872400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>557300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>510300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>399700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>216000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>283200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>231200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>229200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>202900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>242000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-701700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-684000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-714900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-697400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-623500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-524800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-488400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-464000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-439000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-394500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-394900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-370600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-407400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-394500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-400400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-389900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-350800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-341100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-342600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-336400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-328200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-315600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-313400</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>695400</v>
+      </c>
+      <c r="E76" s="3">
         <v>701700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>652100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>652600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>705200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>791300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>810500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>821400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>837900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>880800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>876800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>887700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>342400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>381600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>356100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>357500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>98200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>111900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>104100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>105600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>108500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>118000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E81" s="3">
         <v>30900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-73900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-98700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-36400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-24400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-44600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>36800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-39100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,79 +5611,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E83" s="3">
         <v>16800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>39300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>88900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>95800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>77400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>46200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>49800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>48700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>35900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>9000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-60400</v>
+      </c>
+      <c r="E89" s="3">
         <v>89100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>82100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>74100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>88700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>39900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>42300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>21600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>68600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>30600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-16300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-636800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>51100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>5300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,217 +6775,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-62200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-33200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-51800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-16400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>332700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>355600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>10600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-7500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-800</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-73400</v>
+      </c>
+      <c r="E102" s="3">
         <v>15700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>44100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-89900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>72700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>20400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>28500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>42300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-275400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>350900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>37500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>10100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>162900</v>
+      </c>
+      <c r="E8" s="3">
         <v>149300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>186900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>150100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>152500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>130200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>175400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>145800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>137800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>118100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>161300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>131900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>114500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>60700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>82000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>61000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>42300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>36300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>48500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>37600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>37900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>32400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>41400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E9" s="3">
         <v>65900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>70000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>84900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>130200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>124800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>111000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>65000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>59400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>66800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>63500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>50500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13900</v>
-      </c>
-      <c r="W9" s="3">
-        <v>15100</v>
       </c>
       <c r="X9" s="3">
         <v>15100</v>
       </c>
       <c r="Y9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="Z9" s="3">
         <v>15500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E10" s="3">
         <v>83400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>116900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>65200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>64400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>74000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>72800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>58700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>94500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>68400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>64000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>39900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>60800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>40000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>20800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>35200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>17300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>25900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E12" s="3">
         <v>26700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>22800</v>
       </c>
       <c r="L12" s="3">
         <v>22800</v>
       </c>
       <c r="M12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="N12" s="3">
         <v>20800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1163,65 +1180,68 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>7400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-8300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-5400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1200</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>32000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>11300</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1237,13 +1257,16 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="E15" s="3">
         <v>2900</v>
@@ -1252,67 +1275,70 @@
         <v>2900</v>
       </c>
       <c r="G15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H15" s="3">
         <v>7600</v>
-      </c>
-      <c r="H15" s="3">
-        <v>15400</v>
       </c>
       <c r="I15" s="3">
         <v>15400</v>
       </c>
       <c r="J15" s="3">
+        <v>15400</v>
+      </c>
+      <c r="K15" s="3">
         <v>19200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>23800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>23900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4700</v>
-      </c>
-      <c r="T15" s="3">
-        <v>500</v>
       </c>
       <c r="U15" s="3">
         <v>500</v>
       </c>
       <c r="V15" s="3">
+        <v>500</v>
+      </c>
+      <c r="W15" s="3">
         <v>300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>600</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>500</v>
       </c>
       <c r="Z15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>153300</v>
+      </c>
+      <c r="E17" s="3">
         <v>170500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>143500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>163800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>218900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>222100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>203900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>167000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>161000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>157900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>157700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>155800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>161500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>74500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>74000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>71900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>82900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>47500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>44300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>46500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>45700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>43900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-21200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>43400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-66400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-91900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-21200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-39800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-47000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-10900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-40600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,156 +1545,163 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-12000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>50000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>38300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>47400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>19100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-24300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1900</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>33200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-73200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-99000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-39100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-46600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-29000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-50900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-38800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-87700</v>
-      </c>
-      <c r="P24" s="3">
-        <v>200</v>
       </c>
       <c r="Q24" s="3">
         <v>200</v>
       </c>
       <c r="R24" s="3">
+        <v>200</v>
+      </c>
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-900</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
       </c>
       <c r="X24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-700</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>30900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-73900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-98700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-36400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-44600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-39100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>30900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-73900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-98700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-36400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-44600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>36800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-39100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2240,20 +2301,23 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>10</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>30900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-73900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-98700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-36400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-24400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-44600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-24300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>36800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-39100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>30900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-73900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-98700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-36400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-24400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-44600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-24300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>36800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-39100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>326500</v>
+      </c>
+      <c r="E41" s="3">
         <v>252800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>326200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>310500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>266400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>236600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>326300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>253600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>233100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>204600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>230400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>188200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>193000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>468600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>117700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>103800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>107500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>71300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>88900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>85100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>86100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>80700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>80500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>82400</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2974,87 +3064,93 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
         <v>7500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1122400</v>
+      </c>
+      <c r="E43" s="3">
         <v>999800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1176300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>937200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>908400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>875300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>976500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>804400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>886100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>783000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>927800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>765100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>780500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>401800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>471700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>412400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>292400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>158200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>217600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>172300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>178000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>155900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>205700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>155300</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,156 +3223,165 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E45" s="3">
         <v>20800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1468200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1273500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1523000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1269200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1196900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1137000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1326300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1079300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1141800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1009800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1178100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>974300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1004000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>887800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>607100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>529600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>410200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>236900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>313100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>263200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>270000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>244100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>300500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>260900</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3349,156 +3454,165 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E48" s="3">
         <v>119500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>107900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>110700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>115300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>116800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>123200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>119900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>112100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>107300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>111100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>97400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>83400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>66200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>63300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>61600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>63500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>41100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>45200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>47000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>38800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>41100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>33500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1044800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1051200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1058500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1088500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1168500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1255400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1323800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1361400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1398500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1416600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1455400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1447000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>256500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>264200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>272300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>280000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>34300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>34800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>24200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>24700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,64 +3762,67 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E52" s="3">
         <v>16300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>6700</v>
       </c>
       <c r="F52" s="3">
         <v>6700</v>
       </c>
       <c r="G52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H52" s="3">
         <v>7000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>6900</v>
       </c>
       <c r="M52" s="3">
         <v>6900</v>
       </c>
       <c r="N52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="O52" s="3">
         <v>6100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1900</v>
-      </c>
-      <c r="U52" s="3">
-        <v>2100</v>
       </c>
       <c r="V52" s="3">
         <v>2100</v>
@@ -3714,13 +3834,16 @@
         <v>2100</v>
       </c>
       <c r="Y52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2643200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2454100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2688800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2445000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2407800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2429900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2712200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2529100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2622500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2522500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2712600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2533100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2541300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1214700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>939000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>866500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>757100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>314200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>395100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>335300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>334800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>311400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>360000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,82 +4053,86 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1105600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1357100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1085700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1006600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>934800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1076900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>872700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>953500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>838700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>983100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>806500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>820100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>426700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>496900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>444400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>337700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>188800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>252700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>200900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>207300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>182500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>233500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4006,7 +4140,7 @@
         <v>3700</v>
       </c>
       <c r="E58" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="F58" s="3">
         <v>3600</v>
@@ -4038,8 +4172,8 @@
       <c r="O58" s="3">
         <v>3600</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>10</v>
+      <c r="P58" s="3">
+        <v>3600</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>10</v>
@@ -4056,8 +4190,8 @@
       <c r="U58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -4071,8 +4205,11 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4080,192 +4217,198 @@
         <v>45500</v>
       </c>
       <c r="E59" s="3">
+        <v>45500</v>
+      </c>
+      <c r="F59" s="3">
         <v>41400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>43900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>42700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>45100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>45000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>48800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>50000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>25300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>29200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>24700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1329100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1154700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1402100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1131100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1054000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>982400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1125000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>919000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1002200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>887300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1029400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>858900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>873700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>449000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>522200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>473600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>362300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>202100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>267500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>214500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>220500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>195500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>241000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>202200</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>549000</v>
+      </c>
+      <c r="E61" s="3">
         <v>549100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>533000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>601600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>635000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>674000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>722800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>722100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>721400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>720700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>720000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>719300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>718600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>388600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4293,82 +4436,88 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E62" s="3">
         <v>54900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>52000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>60200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>66100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>68300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>73100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>77500</v>
       </c>
       <c r="K62" s="3">
         <v>77500</v>
       </c>
       <c r="L62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="M62" s="3">
         <v>76500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>82400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>78100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>61300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>34800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>35100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>36700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>37300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1930200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1758700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1987100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1792900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1755200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1724600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1920900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1718600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1801100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1684600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1831900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1656300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1653600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>872400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>557300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>510300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>399700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>216000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>283200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>231200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>229200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>202900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>242000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-702800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-701700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-684000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-714900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-697400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-623500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-524800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-488400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-464000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-439000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-394500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-394900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-370600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-407400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-394500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-400400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-389900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-350800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-341100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-342600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-336400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-328200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-315600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-313400</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E76" s="3">
         <v>695400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>701700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>652100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>652600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>705200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>791300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>810500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>821400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>837900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>880800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>876800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>887700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>342400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>381600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>356100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>357500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>98200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>111900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>104100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>105600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>108500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>118000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>30900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-73900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-98700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-36400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-24400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-44600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-24300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>36800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-39100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,82 +5810,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E83" s="3">
         <v>13600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>88900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>95800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>77400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>46600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>49800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>48700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>35900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>9000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>89600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-60400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>89100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>82100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>74100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>88700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>39900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>42300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>68600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>30600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-16300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>22200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-636800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>51100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>5300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,226 +7021,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-62200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-33200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-51800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-16400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>332700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>355600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>10600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-800</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-73400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>44100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>29800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-89900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>72700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>20400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>28500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>42300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-275400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>350900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>37500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>10100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>MGNI</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E8" s="3">
         <v>162900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>149300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>186900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>150100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>152500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>130200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>175400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>145800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>137800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>118100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>161300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>131900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>114500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>60700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>82000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>61000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>42300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>36300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>48500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>37600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>37900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>41400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E9" s="3">
         <v>62600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>65900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>70000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>84900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>130200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>124800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>111000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>71800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>65000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>59400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>66800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>63500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>50500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13900</v>
-      </c>
-      <c r="X9" s="3">
-        <v>15100</v>
       </c>
       <c r="Y9" s="3">
         <v>15100</v>
       </c>
       <c r="Z9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="AA9" s="3">
         <v>15500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>99500</v>
+      </c>
+      <c r="E10" s="3">
         <v>100300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>83400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>116900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>65200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>22400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K10" s="3">
+        <v>64400</v>
+      </c>
+      <c r="L10" s="3">
+        <v>74000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>72800</v>
+      </c>
+      <c r="N10" s="3">
+        <v>58700</v>
+      </c>
+      <c r="O10" s="3">
+        <v>94500</v>
+      </c>
+      <c r="P10" s="3">
+        <v>68400</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>64000</v>
+      </c>
+      <c r="R10" s="3">
+        <v>39900</v>
+      </c>
+      <c r="S10" s="3">
+        <v>60800</v>
+      </c>
+      <c r="T10" s="3">
+        <v>40000</v>
+      </c>
+      <c r="U10" s="3">
+        <v>20800</v>
+      </c>
+      <c r="V10" s="3">
         <v>22300</v>
       </c>
-      <c r="I10" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>64400</v>
-      </c>
-      <c r="K10" s="3">
-        <v>74000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>72800</v>
-      </c>
-      <c r="M10" s="3">
-        <v>58700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>94500</v>
-      </c>
-      <c r="O10" s="3">
-        <v>68400</v>
-      </c>
-      <c r="P10" s="3">
-        <v>64000</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>39900</v>
-      </c>
-      <c r="R10" s="3">
-        <v>60800</v>
-      </c>
-      <c r="S10" s="3">
-        <v>40000</v>
-      </c>
-      <c r="T10" s="3">
-        <v>20800</v>
-      </c>
-      <c r="U10" s="3">
-        <v>22300</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>35200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>22800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>17300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>25900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>25700</v>
+        <v>20300</v>
       </c>
       <c r="E12" s="3">
-        <v>26700</v>
+        <v>25800</v>
       </c>
       <c r="F12" s="3">
-        <v>23000</v>
+        <v>26900</v>
       </c>
       <c r="G12" s="3">
-        <v>23300</v>
+        <v>23200</v>
       </c>
       <c r="H12" s="3">
-        <v>23200</v>
+        <v>23500</v>
       </c>
       <c r="I12" s="3">
-        <v>24000</v>
+        <v>23400</v>
       </c>
       <c r="J12" s="3">
+        <v>24200</v>
+      </c>
+      <c r="K12" s="3">
         <v>22300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24900</v>
-      </c>
-      <c r="L12" s="3">
-        <v>22800</v>
       </c>
       <c r="M12" s="3">
         <v>22800</v>
       </c>
       <c r="N12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="O12" s="3">
         <v>20800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1183,68 +1200,71 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3">
         <v>7400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-8300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-4200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-5400</v>
       </c>
-      <c r="I14" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>32000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>11300</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
@@ -1260,85 +1280,91 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2800</v>
+        <v>14500</v>
       </c>
       <c r="E15" s="3">
-        <v>2900</v>
+        <v>14200</v>
       </c>
       <c r="F15" s="3">
-        <v>2900</v>
+        <v>13600</v>
       </c>
       <c r="G15" s="3">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="H15" s="3">
-        <v>7600</v>
+        <v>39300</v>
       </c>
       <c r="I15" s="3">
+        <v>88900</v>
+      </c>
+      <c r="J15" s="3">
+        <v>95800</v>
+      </c>
+      <c r="K15" s="3">
         <v>15400</v>
       </c>
-      <c r="J15" s="3">
-        <v>15400</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>19500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>23800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4700</v>
-      </c>
-      <c r="U15" s="3">
-        <v>500</v>
       </c>
       <c r="V15" s="3">
         <v>500</v>
       </c>
       <c r="W15" s="3">
+        <v>500</v>
+      </c>
+      <c r="X15" s="3">
         <v>300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>600</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>500</v>
       </c>
       <c r="AA15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>146900</v>
+      </c>
+      <c r="E17" s="3">
         <v>153300</v>
       </c>
-      <c r="E17" s="3">
-        <v>170500</v>
-      </c>
       <c r="F17" s="3">
-        <v>143500</v>
+        <v>163100</v>
       </c>
       <c r="G17" s="3">
-        <v>163800</v>
+        <v>151800</v>
       </c>
       <c r="H17" s="3">
-        <v>218900</v>
+        <v>167900</v>
       </c>
       <c r="I17" s="3">
-        <v>222100</v>
+        <v>224300</v>
       </c>
       <c r="J17" s="3">
+        <v>223200</v>
+      </c>
+      <c r="K17" s="3">
         <v>203900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>167000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>161000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>157900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>157700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>155800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>161500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>74500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>74000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>71900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>82900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>47000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>47500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>44300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>46500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>45700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>43900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E18" s="3">
         <v>9600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>35100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-71800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="L18" s="3">
         <v>-21200</v>
       </c>
-      <c r="F18" s="3">
-        <v>43400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-66400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-91900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-28500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-39800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-40600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-13300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,185 +1579,192 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="O20" s="3">
         <v>-6000</v>
       </c>
-      <c r="E20" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-6800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-6800</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17800</v>
+        <v>27900</v>
       </c>
       <c r="E21" s="3">
-        <v>-12000</v>
+        <v>24600</v>
       </c>
       <c r="F21" s="3">
-        <v>50000</v>
+        <v>3300</v>
       </c>
       <c r="G21" s="3">
-        <v>20800</v>
+        <v>35400</v>
       </c>
       <c r="H21" s="3">
-        <v>15700</v>
+        <v>24200</v>
       </c>
       <c r="I21" s="3">
-        <v>-3200</v>
+        <v>18800</v>
       </c>
       <c r="J21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K21" s="3">
         <v>38300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>47400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>19700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>19100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-24300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1900</v>
       </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1777,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E23" s="3">
         <v>3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>33200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-73200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-99000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-39100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-29000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-50900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-38800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-87700</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>200</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
       </c>
       <c r="S24" s="3">
+        <v>200</v>
+      </c>
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-900</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
       <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-700</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>30900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-73900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-98700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-36400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-44600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-39100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>30900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-73900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-98700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-36400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-44600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>36800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-39100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2304,20 +2365,23 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>10</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>800</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>10600</v>
+      </c>
+      <c r="L32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N32" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O32" s="3">
         <v>6000</v>
       </c>
-      <c r="E32" s="3">
-        <v>4300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>10300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>6800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>10600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M32" s="3">
-        <v>6800</v>
-      </c>
-      <c r="N32" s="3">
-        <v>6000</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-73900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-98700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-36400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-24400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-44600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>36800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-39100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>30900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-73900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-98700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-36400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-24400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-44600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>36800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-39100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,85 +3004,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>387200</v>
+      </c>
+      <c r="E41" s="3">
         <v>326500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>252800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>326200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>310500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>266400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>236600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>326300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>253600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>233100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>204600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>230400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>188200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>193000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>468600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>117700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>103800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>107500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>71300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>88900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>85100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>86100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>80700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>80500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>82400</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3067,113 +3157,119 @@
         <v>0</v>
       </c>
       <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
         <v>7500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1163800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1122400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>999800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1176300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>937200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>908400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>875300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>976500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>804400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>886100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>783000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>927800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>765100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>780500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>401800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>471700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>412400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>292400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>158200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>217600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>172300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>178000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>155900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>205700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>155300</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3226,185 +3322,194 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>19400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>20800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>20500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>21500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>22100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>25100</v>
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J45" s="3">
+        <v>700</v>
+      </c>
+      <c r="K45" s="3">
         <v>23500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1573400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1468200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1273500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1523000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1269200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1196900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1137000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1326300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1079300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1141800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1009800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1178100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>974300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1004000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>887800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>607100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>529600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>410200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>236900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>313100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>263200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>270000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>244100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>300500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>260900</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3457,162 +3562,171 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>122100</v>
+      </c>
+      <c r="E48" s="3">
         <v>125000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>119500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>107900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>110700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>115300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>116800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>123200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>119900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>112100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>107300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>111100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>97400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>83400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>66200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>63300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>61600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>63500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>41100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>45200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>47000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>38800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>41100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>33500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1033200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1039000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1044800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1051200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1058500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1088500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1168500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1255400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1323800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1361400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1398500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1416600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1455400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1447000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>256500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>264200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>272300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>280000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>34300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>34800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>24200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>24700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,67 +3882,70 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E52" s="3">
         <v>11000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H52" s="3">
         <v>6700</v>
       </c>
-      <c r="G52" s="3">
-        <v>6700</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7000</v>
       </c>
-      <c r="I52" s="3">
-        <v>7600</v>
-      </c>
       <c r="J52" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K52" s="3">
         <v>7400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>6900</v>
       </c>
       <c r="N52" s="3">
         <v>6900</v>
       </c>
       <c r="O52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="P52" s="3">
         <v>6100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1900</v>
-      </c>
-      <c r="V52" s="3">
-        <v>2100</v>
       </c>
       <c r="W52" s="3">
         <v>2100</v>
@@ -3837,13 +3957,16 @@
         <v>2100</v>
       </c>
       <c r="Z52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2737900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2643200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2454100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2688800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2445000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2407800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2429900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2712200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2529100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2622500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2522500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2712600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2533100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2541300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1214700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>939000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>866500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>757100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>314200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>395100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>335300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>334800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>311400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>360000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,108 +4184,112 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1366500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1280000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1105600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1357100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1085700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1006600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>934800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1076900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>872700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>953500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>838700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>983100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>806500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>820100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>426700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>496900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>444400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>337700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>188800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>252700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>200900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>207300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>182500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>233500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3700</v>
+        <v>21900</v>
       </c>
       <c r="E58" s="3">
-        <v>3700</v>
+        <v>23700</v>
       </c>
       <c r="F58" s="3">
-        <v>3600</v>
+        <v>23600</v>
       </c>
       <c r="G58" s="3">
-        <v>3600</v>
+        <v>24000</v>
       </c>
       <c r="H58" s="3">
-        <v>3600</v>
+        <v>24500</v>
       </c>
       <c r="I58" s="3">
-        <v>3600</v>
+        <v>25100</v>
       </c>
       <c r="J58" s="3">
-        <v>3600</v>
+        <v>24500</v>
       </c>
       <c r="K58" s="3">
         <v>3600</v>
@@ -4175,8 +4309,8 @@
       <c r="P58" s="3">
         <v>3600</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>10</v>
+      <c r="Q58" s="3">
+        <v>3600</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>10</v>
@@ -4193,8 +4327,8 @@
       <c r="V58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4208,210 +4342,219 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>45500</v>
+        <v>7000</v>
       </c>
       <c r="E59" s="3">
-        <v>45500</v>
+        <v>6200</v>
       </c>
       <c r="F59" s="3">
-        <v>41400</v>
+        <v>7700</v>
       </c>
       <c r="G59" s="3">
-        <v>41700</v>
+        <v>6000</v>
       </c>
       <c r="H59" s="3">
-        <v>43900</v>
+        <v>5800</v>
       </c>
       <c r="I59" s="3">
-        <v>44000</v>
+        <v>6600</v>
       </c>
       <c r="J59" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K59" s="3">
         <v>44500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>42700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>45100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>45000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>50000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>25300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>29200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>24700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1413600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1329100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1154700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1402100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1131100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1054000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>982400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1125000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>919000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1002200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>887300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1029400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>858900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>873700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>449000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>522200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>473600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>362300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>202100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>267500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>214500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>220500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>195500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>241000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>202200</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>549000</v>
+        <v>596700</v>
       </c>
       <c r="E61" s="3">
-        <v>549100</v>
+        <v>599300</v>
       </c>
       <c r="F61" s="3">
-        <v>533000</v>
+        <v>602100</v>
       </c>
       <c r="G61" s="3">
-        <v>601600</v>
+        <v>582700</v>
       </c>
       <c r="H61" s="3">
-        <v>635000</v>
+        <v>655600</v>
       </c>
       <c r="I61" s="3">
-        <v>674000</v>
+        <v>693900</v>
       </c>
       <c r="J61" s="3">
+        <v>735600</v>
+      </c>
+      <c r="K61" s="3">
         <v>722800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>722100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>721400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>720700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>720000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>719300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>718600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>388600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4439,85 +4582,91 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>52100</v>
+        <v>1600</v>
       </c>
       <c r="E62" s="3">
-        <v>54900</v>
+        <v>1500</v>
       </c>
       <c r="F62" s="3">
-        <v>52000</v>
+        <v>1600</v>
       </c>
       <c r="G62" s="3">
-        <v>60200</v>
+        <v>1700</v>
       </c>
       <c r="H62" s="3">
-        <v>66100</v>
+        <v>1800</v>
       </c>
       <c r="I62" s="3">
-        <v>68300</v>
+        <v>1800</v>
       </c>
       <c r="J62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K62" s="3">
         <v>73100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>77500</v>
       </c>
       <c r="L62" s="3">
         <v>77500</v>
       </c>
       <c r="M62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="N62" s="3">
         <v>76500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>82400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>78100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>61300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>34800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>35100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>36700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>37300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>15700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2012000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1930200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1758700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1987100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1792900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1755200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1724600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1920900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1718600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1801100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1684600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1831900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1656300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1653600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>872400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>557300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>510300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>399700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>216000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>283200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>231200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>229200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>202900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>242000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-697600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-702800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-701700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-684000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-714900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-697400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-623500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-524800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-488400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-464000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-439000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-394500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-394900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-370600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-407400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-394500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-400400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-389900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-350800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-341100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-342600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-336400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-328200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-315600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-313400</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>725900</v>
+      </c>
+      <c r="E76" s="3">
         <v>713000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>695400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>701700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>652100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>652600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>705200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>791300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>810500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>821400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>837900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>880800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>876800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>887700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>342400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>381600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>356100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>357500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>98200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>111900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>104100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>105600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>108500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>118000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>30900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-73900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-98700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-36400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-24400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-44600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>36800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-39100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,85 +6009,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>14200</v>
+        <v>9500</v>
       </c>
       <c r="E83" s="3">
-        <v>13600</v>
+        <v>10200</v>
       </c>
       <c r="F83" s="3">
-        <v>16800</v>
+        <v>9400</v>
       </c>
       <c r="G83" s="3">
-        <v>39300</v>
+        <v>64800</v>
       </c>
       <c r="H83" s="3">
-        <v>88900</v>
+        <v>8600</v>
       </c>
       <c r="I83" s="3">
-        <v>95800</v>
+        <v>7400</v>
       </c>
       <c r="J83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K83" s="3">
         <v>77400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>46200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>49800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>48700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>35900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>9000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E89" s="3">
         <v>89600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-60400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>89100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>82100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>74100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>88700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>39900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>42300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>68600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>30600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-16300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>22200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-13300</v>
+        <v>-14000</v>
       </c>
       <c r="E91" s="3">
-        <v>-9300</v>
+        <v>-9200</v>
       </c>
       <c r="F91" s="3">
-        <v>-12000</v>
+        <v>-5900</v>
       </c>
       <c r="G91" s="3">
-        <v>-6800</v>
+        <v>-9600</v>
       </c>
       <c r="H91" s="3">
-        <v>-11100</v>
+        <v>-4400</v>
       </c>
       <c r="I91" s="3">
-        <v>-7500</v>
+        <v>-8300</v>
       </c>
       <c r="J91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-15200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-31300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-636800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>51100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>5300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,31 +6949,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,235 +7267,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-62200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-30600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-33200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-51800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-16400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>332700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>355600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>10600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-800</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>300</v>
+      </c>
+      <c r="G101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J101" s="3">
+        <v>300</v>
+      </c>
+      <c r="K101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N101" s="3">
+        <v>300</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F101" s="3">
-        <v>800</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="Q101" s="3">
+        <v>100</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S101" s="3">
+        <v>900</v>
+      </c>
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="M101" s="3">
-        <v>300</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W101" s="3">
+        <v>200</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="P101" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>900</v>
-      </c>
-      <c r="S101" s="3">
-        <v>300</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="V101" s="3">
-        <v>200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E102" s="3">
         <v>73600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-73400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>15700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>44100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>29800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-89900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>72700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>28500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>42300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-275400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>350900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>37500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>10100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>MGNI</t>
   </si>
@@ -656,365 +656,377 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E8" s="3">
         <v>162000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>162900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>149300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>186900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>150100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>152500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>130200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>175400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>145800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>137800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>118100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>161300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>131900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>114500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>60700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>82000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>61000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>42300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>36300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>48500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>37600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>37900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>32400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>41400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E9" s="3">
         <v>62500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>62600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>65900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>70000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>84900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>130200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>124800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>111000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>71800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>65000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>59400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>66800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>63500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>50500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13900</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>15100</v>
       </c>
       <c r="Z9" s="3">
         <v>15100</v>
       </c>
       <c r="AA9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="AB9" s="3">
         <v>15500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E10" s="3">
         <v>99500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>83400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>116900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>65200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>64400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>74000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>72800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>58700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>94500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>68400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>64000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>39900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>60800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>40000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>20800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>35200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>22800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>17300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>25900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1055,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E12" s="3">
         <v>20300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24900</v>
-      </c>
-      <c r="M12" s="3">
-        <v>22800</v>
       </c>
       <c r="N12" s="3">
         <v>22800</v>
       </c>
       <c r="O12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="P12" s="3">
         <v>20800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,71 +1219,74 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-8300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-4200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1100</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>32000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>11300</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
@@ -1283,88 +1302,94 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E15" s="3">
         <v>14500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>39300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>88900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>95800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>15400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>19300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>23900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4700</v>
-      </c>
-      <c r="V15" s="3">
-        <v>500</v>
       </c>
       <c r="W15" s="3">
         <v>500</v>
       </c>
       <c r="X15" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y15" s="3">
         <v>300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>600</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>500</v>
       </c>
       <c r="AB15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>153800</v>
+      </c>
+      <c r="E17" s="3">
         <v>146900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>153300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>163100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>151800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>167900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>224300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>223200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>203900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>167000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>161000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>157900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>157700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>155800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>161500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>74500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>74000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>71900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>82900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>47000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>47500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>44300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>46500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>45700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>43900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E18" s="3">
         <v>15100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>35100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-17800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-71800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-93000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-39800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-47000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-40600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-13300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,195 +1612,202 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E21" s="3">
         <v>27900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>24600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>35400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>24200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>38300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>47400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>19700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>19100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-24300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1900</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
       <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>6800</v>
+        <v>5400</v>
       </c>
       <c r="E22" s="3">
         <v>6800</v>
       </c>
       <c r="F22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="G22" s="3">
         <v>8000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8200</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1820,168 +1859,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E23" s="3">
         <v>6200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>33200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-73200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-99000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-39100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-46600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-50900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-38800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-13300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-87700</v>
-      </c>
-      <c r="R24" s="3">
-        <v>200</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
       </c>
       <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-900</v>
-      </c>
-      <c r="X24" s="3">
-        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>100</v>
       </c>
       <c r="Z24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>100</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E26" s="3">
         <v>5200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-73900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-98700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-36400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-44600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-39100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E27" s="3">
         <v>5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>30900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-73900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-98700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-36400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-44600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>36800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-39100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2368,20 +2428,23 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2606,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E33" s="3">
         <v>5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-73900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-98700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-36400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-44600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>36800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-39100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E35" s="3">
         <v>5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-73900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-98700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-36400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-44600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>36800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-39100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3090,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>483200</v>
+      </c>
+      <c r="E41" s="3">
         <v>387200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>326500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>252800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>326200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>310500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>266400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>236600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>326300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>253600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>233100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>204600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>230400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>188200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>193000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>468600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>117700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>103800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>107500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>71300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>88900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>85100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>86100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>80700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>80500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>82400</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3160,93 +3249,99 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
         <v>7500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1163800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1122400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>999800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1176300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>937200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>908400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>875300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>976500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>804400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>886100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>783000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>927800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>765100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>780500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>401800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>471700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>412400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>292400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>158200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>217600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>172300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>178000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>155900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>205700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>155300</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3271,8 +3366,8 @@
       <c r="J44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3325,8 +3420,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3348,145 +3446,151 @@
       <c r="I45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>23500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>30600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1703200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1573400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1468200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1273500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1523000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1269200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1196900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1137000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1326300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1079300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1141800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1009800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1178100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>974300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1004000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>887800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>607100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>529600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>410200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>236900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>313100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>263200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>270000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>244100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>300500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>260900</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3511,8 +3615,8 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3565,168 +3669,177 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>119100</v>
+      </c>
+      <c r="E48" s="3">
         <v>122100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>125000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>119500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>107900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>110700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>115300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>116800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>123200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>119900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>112100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>107300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>111100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>97400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>83400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>66200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>63300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>61600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>63500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>41100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>45200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>47000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>38800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>33500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1026200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1033200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1039000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1044800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1051200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1058500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1088500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1168500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1255400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1323800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1361400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1398500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1416600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1455400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1447000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>256500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>264200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>272300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>280000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>34300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>34800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>24200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>24700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,70 +4001,73 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E52" s="3">
         <v>9100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7200</v>
-      </c>
-      <c r="N52" s="3">
-        <v>6900</v>
       </c>
       <c r="O52" s="3">
         <v>6900</v>
       </c>
       <c r="P52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Q52" s="3">
         <v>6100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1900</v>
-      </c>
-      <c r="W52" s="3">
-        <v>2100</v>
       </c>
       <c r="X52" s="3">
         <v>2100</v>
@@ -3960,13 +4079,16 @@
         <v>2100</v>
       </c>
       <c r="AA52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4167,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2854800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2737900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2643200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2454100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2688800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2445000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2407800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2429900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2712200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2529100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2622500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2522500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2712600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2533100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2541300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1214700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>939000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>866500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>757100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>314200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>395100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>335300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>334800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>311400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>360000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,114 +4314,118 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1448700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1366500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1280000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1105600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1357100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1085700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1006600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>934800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1076900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>872700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>953500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>838700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>983100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>806500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>820100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>426700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>496900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>444400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>337700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>188800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>252700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>200900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>207300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>182500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>233500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E58" s="3">
         <v>21900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>24000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>25100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>24500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>3600</v>
       </c>
       <c r="L58" s="3">
         <v>3600</v>
@@ -4312,8 +4445,8 @@
       <c r="Q58" s="3">
         <v>3600</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>10</v>
+      <c r="R58" s="3">
+        <v>3600</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>10</v>
@@ -4330,8 +4463,8 @@
       <c r="W58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4345,219 +4478,228 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E59" s="3">
         <v>7000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>44500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>45100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>45000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>42700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>50000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>25300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>29200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1496000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1413600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1329100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1154700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1402100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1131100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1054000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>982400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1125000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>919000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1002200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>887300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1029400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>858900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>873700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>449000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>522200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>473600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>362300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>202100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>267500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>214500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>220500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>195500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>241000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>202200</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>589100</v>
+      </c>
+      <c r="E61" s="3">
         <v>596700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>599300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>602100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>582700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>655600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>693900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>735600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>722800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>722100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>721400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>720700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>720000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>719300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>718600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>388600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4585,88 +4727,94 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
-        <v>1700</v>
-      </c>
       <c r="H62" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="I62" s="3">
         <v>1800</v>
       </c>
       <c r="J62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>73100</v>
-      </c>
-      <c r="L62" s="3">
-        <v>77500</v>
       </c>
       <c r="M62" s="3">
         <v>77500</v>
       </c>
       <c r="N62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="O62" s="3">
         <v>76500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>82400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>78100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>61300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>34800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>35100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>36700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>37300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>15700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5059,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2086600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2012000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1930200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1758700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1987100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1792900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1755200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1724600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1920900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1718600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1801100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1684600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1831900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1656300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1653600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>872400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>557300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>510300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>399700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>216000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>283200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>231200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>229200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>202900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>242000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5505,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-661200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-697600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-702800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-701700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-684000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-714900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-697400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-623500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-524800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-488400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-464000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-439000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-394500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-394900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-370600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-407400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-394500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-400400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-389900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-350800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-341100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-342600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-336400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-328200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-315600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-313400</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5837,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>768200</v>
+      </c>
+      <c r="E76" s="3">
         <v>725900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>713000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>695400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>701700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>652100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>652600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>705200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>791300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>810500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>821400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>837900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>880800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>876800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>887700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>342400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>381600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>356100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>357500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>98200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>111900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>104100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>105600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>108500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>118000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E81" s="3">
         <v>5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-73900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-98700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-36400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-44600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>36800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-39100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,88 +6207,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E83" s="3">
         <v>9500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>64800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>7400</v>
       </c>
       <c r="J83" s="3">
         <v>7400</v>
       </c>
       <c r="K83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="L83" s="3">
         <v>77400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>46600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>46200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>49800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>48700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>35900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>9000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6703,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>114700</v>
+      </c>
+      <c r="E89" s="3">
         <v>91300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>89600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-60400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>89100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>82100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>74100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>88700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>39900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>42300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>30600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-16300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>22200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6819,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7066,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-31300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-636800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>51100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>5300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6976,8 +7209,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7030,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,244 +7512,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-62200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-30600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-33200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-51800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-16400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>332700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>355600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>10600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-800</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E102" s="3">
         <v>60800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>73600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-73400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>44100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>29800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-89900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>72700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>28500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>42300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-275400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>350900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>37500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-17600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>10100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>MGNI</t>
   </si>
@@ -656,377 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>155800</v>
+      </c>
+      <c r="E8" s="3">
         <v>194000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>162000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>162900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>149300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>186900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>150100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>152500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>130200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>175400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>145800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>137800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>118100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>161300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>131900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>114500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>60700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>82000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>61000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>42300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>36300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>48500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>37600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>37900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>32400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>41400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E9" s="3">
         <v>67800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>62500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>62600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>65900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>70000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>84900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>130200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>124800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>111000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>71800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>65000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>59400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>66800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>63500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>50500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>21500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13900</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>15100</v>
       </c>
       <c r="AA9" s="3">
         <v>15100</v>
       </c>
       <c r="AB9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="AC9" s="3">
         <v>15500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E10" s="3">
         <v>126200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>99500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>83400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>116900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>65200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>64400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>74000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>72800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>58700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>94500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>68400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>64000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>39900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>60800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>40000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>20800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>35200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>17300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>25900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,8 +1069,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1065,82 +1079,85 @@
         <v>22300</v>
       </c>
       <c r="E12" s="3">
+        <v>22300</v>
+      </c>
+      <c r="F12" s="3">
         <v>20300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24900</v>
-      </c>
-      <c r="N12" s="3">
-        <v>22800</v>
       </c>
       <c r="O12" s="3">
         <v>22800</v>
       </c>
       <c r="P12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="Q12" s="3">
         <v>20800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1222,74 +1239,77 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-8300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1100</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>32000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>11300</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
@@ -1305,91 +1325,97 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E15" s="3">
         <v>4200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>39300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>88900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>95800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>15400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>19200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>19500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>23800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>23900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4700</v>
-      </c>
-      <c r="W15" s="3">
-        <v>500</v>
       </c>
       <c r="X15" s="3">
         <v>500</v>
       </c>
       <c r="Y15" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z15" s="3">
         <v>300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>600</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>500</v>
       </c>
       <c r="AC15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E17" s="3">
         <v>153800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>146900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>153300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>163100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>151800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>167900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>224300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>223200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>203900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>167000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>161000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>157900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>157700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>155800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>161500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>74500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>74000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>71900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>82900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>47000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>47500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>44300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>46500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>45700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>43900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>40200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>35100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-17800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-71800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-93000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-39800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-23900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-47000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-40600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-13300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,204 +1646,211 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E21" s="3">
         <v>51900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>27900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>24600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>35400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>38300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>47400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>19700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>19100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-24300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1900</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E22" s="3">
         <v>5400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>6800</v>
       </c>
       <c r="F22" s="3">
         <v>6800</v>
       </c>
       <c r="G22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H22" s="3">
         <v>8000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8200</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1862,174 +1902,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E23" s="3">
         <v>42300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>33200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-73200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-99000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-39100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-46600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-29000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-50900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-12700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-38800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E24" s="3">
         <v>5900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-87700</v>
-      </c>
-      <c r="S24" s="3">
-        <v>200</v>
       </c>
       <c r="T24" s="3">
         <v>200</v>
       </c>
       <c r="U24" s="3">
+        <v>200</v>
+      </c>
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>100</v>
       </c>
       <c r="AA24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>100</v>
       </c>
       <c r="AC24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E26" s="3">
         <v>36400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>30900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-73900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-98700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-36400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-44600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>36800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-12900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-39100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E27" s="3">
         <v>36400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>30900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-73900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-98700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-36400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-44600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>36800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-12900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-39100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2431,20 +2492,23 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,174 +2676,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>7500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E33" s="3">
         <v>36400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>30900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-73900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-98700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-36400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-44600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>36800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-12900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-39100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E35" s="3">
         <v>36400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>30900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-73900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-98700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-36400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-44600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>36800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-12900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-39100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,91 +3177,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>429700</v>
+      </c>
+      <c r="E41" s="3">
         <v>483200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>387200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>326500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>252800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>326200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>310500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>266400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>236600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>326300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>253600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>233100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>204600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>230400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>188200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>193000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>468600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>117700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>103800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>107500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>71300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>88900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>85100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>86100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>80700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>80500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>82400</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3252,96 +3342,102 @@
         <v>0</v>
       </c>
       <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>7500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1053200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1163800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1122400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>999800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1176300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>937200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>908400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>875300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>976500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>804400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>886100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>783000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>927800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>765100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>780500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>401800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>471700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>412400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>292400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>158200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>217600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>172300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>178000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>155900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>205700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>155300</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3369,8 +3465,8 @@
       <c r="K44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3423,8 +3519,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3449,148 +3548,154 @@
       <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>23500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>21000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>30600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1515100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1703200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1573400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1468200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1273500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1523000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1269200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1196900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1137000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1326300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1079300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1141800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1009800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1178100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>974300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1004000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>887800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>607100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>529600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>410200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>236900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>313100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>263200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>270000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>244100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>300500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>260900</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3618,8 +3723,8 @@
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3672,174 +3777,183 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E48" s="3">
         <v>119100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>122100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>125000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>119500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>107900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>110700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>115300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>116800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>123200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>119900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>112100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>107300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>111100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>97400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>83400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>66200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>63300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>61600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>63500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>41100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>45200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>47000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>38800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>41100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>33500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1018800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1026200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1033200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1039000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1044800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1051200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1058500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1088500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1168500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1255400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1323800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1361400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1398500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1416600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1455400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1447000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>256500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>264200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>272300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>280000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>34300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>34800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>24200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>24700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,73 +4121,76 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E52" s="3">
         <v>6100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>6900</v>
       </c>
       <c r="P52" s="3">
         <v>6900</v>
       </c>
       <c r="Q52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="R52" s="3">
         <v>6100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1900</v>
-      </c>
-      <c r="X52" s="3">
-        <v>2100</v>
       </c>
       <c r="Y52" s="3">
         <v>2100</v>
@@ -4082,13 +4202,16 @@
         <v>2100</v>
       </c>
       <c r="AB52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,91 +4293,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2674700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2854800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2737900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2643200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2454100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2688800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2445000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2407800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2429900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2712200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2529100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2622500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2522500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2712600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2533100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2541300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1214700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>939000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>866500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>757100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>314200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>395100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>335300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>334800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>311400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>360000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,120 +4445,124 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1284200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1448700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1366500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1280000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1105600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1357100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1085700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1006600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>934800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1076900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>872700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>953500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>838700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>983100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>806500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>820100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>426700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>496900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>444400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>337700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>188800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>252700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>200900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>207300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>182500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>233500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>223800</v>
+      </c>
+      <c r="E58" s="3">
         <v>19700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>25100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24500</v>
-      </c>
-      <c r="L58" s="3">
-        <v>3600</v>
       </c>
       <c r="M58" s="3">
         <v>3600</v>
@@ -4448,8 +4582,8 @@
       <c r="R58" s="3">
         <v>3600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>10</v>
+      <c r="S58" s="3">
+        <v>3600</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>10</v>
@@ -4466,8 +4600,8 @@
       <c r="X58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4481,228 +4615,237 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E59" s="3">
         <v>9900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>44500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>45100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>45000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>48800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>50000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>25300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>29200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>24700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1538500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1496000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1413600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1329100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1154700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1402100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1131100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1054000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>982400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1125000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>919000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1002200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>887300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1029400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>858900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>873700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>449000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>522200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>473600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>362300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>202100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>267500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>214500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>220500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>195500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>241000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>202200</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>392800</v>
+      </c>
+      <c r="E61" s="3">
         <v>589100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>596700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>599300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>602100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>582700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>655600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>693900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>735600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>722800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>722100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>721400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>720700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>720000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>719300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>718600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>388600</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4730,91 +4873,97 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1600</v>
       </c>
       <c r="H62" s="3">
         <v>1600</v>
       </c>
       <c r="I62" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="J62" s="3">
         <v>1800</v>
       </c>
       <c r="K62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>73100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>77500</v>
       </c>
       <c r="N62" s="3">
         <v>77500</v>
       </c>
       <c r="O62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="P62" s="3">
         <v>76500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>82400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>78100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>61300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>34800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>35100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>36700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>37300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>15700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>16700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,91 +5217,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1932900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2086600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2012000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1930200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1758700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1987100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1792900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1755200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1724600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1920900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1718600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1801100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1684600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1831900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1656300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1653600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>872400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>557300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>510300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>399700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>216000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>283200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>231200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>229200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>202900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>242000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,91 +5679,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-670800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-661200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-697600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-702800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-701700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-684000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-714900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-697400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-623500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-524800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-488400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-464000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-439000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-394500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-394900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-370600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-407400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-394500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-400400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-389900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-350800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-341100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-342600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-336400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-328200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-315600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-313400</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,91 +6023,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>741800</v>
+      </c>
+      <c r="E76" s="3">
         <v>768200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>725900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>713000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>695400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>701700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>652100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>652600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>705200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>791300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>810500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>821400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>837900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>880800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>876800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>887700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>342400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>381600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>356100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>357500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>98200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>111900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>104100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>105600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>108500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>118000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E81" s="3">
         <v>36400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>30900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-73900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-98700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-36400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-44600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>36800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-12900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-39100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,91 +6406,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>64800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>7400</v>
       </c>
       <c r="K83" s="3">
         <v>7400</v>
       </c>
       <c r="L83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="M83" s="3">
         <v>77400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>46600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>46200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>49800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>48700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>35900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +6920,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E89" s="3">
         <v>114700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>91300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>89600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-60400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>89100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>82100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>74100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>39900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>42300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>68600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>30600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-16300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>22200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,91 +7040,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,91 +7296,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-35500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-636800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>51100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>5300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7212,8 +7446,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,253 +7758,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-62200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-33200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-51800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-16400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>332700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>355600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>10600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-800</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-53500</v>
+      </c>
+      <c r="E102" s="3">
         <v>96000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>60800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>73600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-73400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>44100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>29800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-89900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>72700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>28500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-25800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>42300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-275400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>350900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>12600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>37500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-17600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>10100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>MGNI</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>173300</v>
+      </c>
+      <c r="E8" s="3">
         <v>155800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>194000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>162000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>162900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>186900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>150100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>152500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>130200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>175400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>145800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>137800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>118100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>161300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>131900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>114500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>60700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>82000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>61000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>42300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>36300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>48500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>37600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>37900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>41400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E9" s="3">
         <v>62800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>67800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>62500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>62600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>65900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>70000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>84900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>130200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>124800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>111000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>71800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>65000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>59400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>66800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>63500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>50500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>21000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>21500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13900</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>15100</v>
       </c>
       <c r="AB9" s="3">
         <v>15100</v>
       </c>
       <c r="AC9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="AD9" s="3">
         <v>15500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>108400</v>
+      </c>
+      <c r="E10" s="3">
         <v>93000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>126200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>99500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>100300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>83400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>116900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>65200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>64400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>74000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>72800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>58700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>94500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>68400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>64000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>39900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>60800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>40000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>20800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>22300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>35200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>23700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>17300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>25900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>22300</v>
+        <v>21600</v>
       </c>
       <c r="E12" s="3">
         <v>22300</v>
       </c>
       <c r="F12" s="3">
+        <v>22300</v>
+      </c>
+      <c r="G12" s="3">
         <v>20300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>25800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24900</v>
-      </c>
-      <c r="O12" s="3">
-        <v>22800</v>
       </c>
       <c r="P12" s="3">
         <v>22800</v>
       </c>
       <c r="Q12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="R12" s="3">
         <v>20800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>8600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1242,77 +1259,80 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-8300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1100</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>32000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>11300</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
@@ -1328,94 +1348,100 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E15" s="3">
         <v>15600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>39300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>88900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>95800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>15400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>19300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>19500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>23800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>23900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4700</v>
-      </c>
-      <c r="X15" s="3">
-        <v>500</v>
       </c>
       <c r="Y15" s="3">
         <v>500</v>
       </c>
       <c r="Z15" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA15" s="3">
         <v>300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>600</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>500</v>
       </c>
       <c r="AD15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>151400</v>
+      </c>
+      <c r="E17" s="3">
         <v>157100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>153800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>146900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>153300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>163100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>151800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>167900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>224300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>223200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>203900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>167000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>161000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>157900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>157700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>155800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>161500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>74500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>74000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>71900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>82900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>47000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>47500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>44300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>46500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>45700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>43900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>40200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>35100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-71800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-93000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-23900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-47000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-13800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-40600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-13300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,213 +1680,220 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E20" s="3">
         <v>1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E21" s="3">
         <v>12400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>51900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>27900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>24600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>35400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>21100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>47400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>19700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-15000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>19100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-24300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1900</v>
       </c>
-      <c r="AA21" s="3">
-        <v>0</v>
-      </c>
       <c r="AB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E22" s="3">
         <v>5200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>6800</v>
       </c>
       <c r="G22" s="3">
         <v>6800</v>
       </c>
       <c r="H22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I22" s="3">
         <v>8000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8200</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1905,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>42300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-25600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>33200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-73200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-99000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-39100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-25100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-29000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-50900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-38800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-13300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-87700</v>
-      </c>
-      <c r="T24" s="3">
-        <v>200</v>
       </c>
       <c r="U24" s="3">
         <v>200</v>
       </c>
       <c r="V24" s="3">
+        <v>200</v>
+      </c>
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-900</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
       </c>
       <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-700</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>100</v>
       </c>
       <c r="AD24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>36400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-73900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-98700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-36400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-24300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>36800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-12900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-39100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>36400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>30900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-73900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-98700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-36400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-24300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>36800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-12900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-39100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2495,20 +2556,23 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>10</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>36400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>30900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-73900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-98700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-36400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-24400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-24300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>36800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-12900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-39100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>36400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>30900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-73900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-98700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-36400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-24400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-24300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>36800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-12900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-39100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>426000</v>
+      </c>
+      <c r="E41" s="3">
         <v>429700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>483200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>387200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>326500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>252800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>326200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>310500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>266400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>236600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>326300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>253600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>233100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>204600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>230400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>188200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>193000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>468600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>117700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>103800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>107500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>71300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>88900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>85100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>86100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>80700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>80500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>82400</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3345,99 +3435,105 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>7500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1303000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1053200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1163800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1122400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>999800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1176300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>937200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>908400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>875300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>976500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>804400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>886100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>783000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>927800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>765100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>780500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>401800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>471700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>412400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>292400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>158200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>217600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>172300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>178000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>155900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>205700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>155300</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3468,8 +3564,8 @@
       <c r="L44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3522,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3551,151 +3650,157 @@
       <c r="K45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>21000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>30600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>13400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1756500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1515100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1703200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1573400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1468200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1273500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1523000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1269200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1196900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1137000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1326300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1079300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1141800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1009800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1178100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>974300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1004000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>887800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>607100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>529600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>410200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>236900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>313100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>263200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>270000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>244100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>300500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>260900</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3726,8 +3831,8 @@
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3780,180 +3885,189 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>147900</v>
+      </c>
+      <c r="E48" s="3">
         <v>134900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>119100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>122100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>125000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>119500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>107900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>110700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>115300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>116800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>123200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>119900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>112100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>107300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>111100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>97400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>83400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>66200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>63300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>61600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>63500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>41100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>45200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>47000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>38800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>41100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>33500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1016500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1018800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1026200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1033200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1039000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1044800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1051200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1058500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1088500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1168500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1255400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1323800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1361400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1398500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1416600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1455400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1447000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>256500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>264200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>272300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>280000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>34300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>34800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>23800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>24200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>24700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,76 +4241,79 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
         <v>5900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7200</v>
-      </c>
-      <c r="P52" s="3">
-        <v>6900</v>
       </c>
       <c r="Q52" s="3">
         <v>6900</v>
       </c>
       <c r="R52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="S52" s="3">
         <v>6100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1900</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>2100</v>
       </c>
       <c r="Z52" s="3">
         <v>2100</v>
@@ -4205,13 +4325,16 @@
         <v>2100</v>
       </c>
       <c r="AC52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2927100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2674700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2854800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2737900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2643200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2454100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2688800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2445000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2407800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2429900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2712200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2529100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2622500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2522500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2712600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2533100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2541300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1214700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>939000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>866500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>757100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>314200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>395100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>335300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>334800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>311400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>360000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,126 +4576,130 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1508200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1284200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1448700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1366500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1280000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1105600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1357100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1085700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1006600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>934800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1076900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>872700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>953500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>838700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>983100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>806500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>820100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>426700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>496900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>444400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>337700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>188800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>252700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>200900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>207300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>182500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>233500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>227300</v>
+      </c>
+      <c r="E58" s="3">
         <v>223800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>23600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>24500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>25100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24500</v>
-      </c>
-      <c r="M58" s="3">
-        <v>3600</v>
       </c>
       <c r="N58" s="3">
         <v>3600</v>
@@ -4585,8 +4719,8 @@
       <c r="S58" s="3">
         <v>3600</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>10</v>
+      <c r="T58" s="3">
+        <v>3600</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>10</v>
@@ -4603,8 +4737,8 @@
       <c r="Y58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4618,237 +4752,246 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E59" s="3">
         <v>8200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>44500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>45100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>45000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>48800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>50000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>25300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>29200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>24700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1765000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1538500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1496000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1413600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1329100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1154700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1402100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1131100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1054000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>982400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1125000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>919000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1002200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>887300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1029400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>858900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>873700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>449000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>522200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>473600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>362300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>202100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>267500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>214500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>220500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>195500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>241000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>202200</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>392000</v>
+      </c>
+      <c r="E61" s="3">
         <v>392800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>589100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>596700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>599300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>602100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>582700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>655600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>693900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>735600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>722800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>722100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>721400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>720700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>720000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>719300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>718600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>388600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4876,94 +5019,100 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1600</v>
       </c>
       <c r="I62" s="3">
         <v>1600</v>
       </c>
       <c r="J62" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="K62" s="3">
         <v>1800</v>
       </c>
       <c r="L62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M62" s="3">
         <v>2000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>73100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>77500</v>
       </c>
       <c r="O62" s="3">
         <v>77500</v>
       </c>
       <c r="P62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="Q62" s="3">
         <v>76500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>82400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>78100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>61300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>34800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>35100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>36700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>37300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>15700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>16700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2158700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1932900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2086600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2012000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1930200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1758700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1987100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1792900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1755200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1724600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1920900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1718600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1801100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1684600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1831900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1656300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1653600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>872400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>557300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>510300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>399700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>216000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>283200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>231200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>229200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>202900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>242000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-659700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-670800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-661200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-697600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-702800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-701700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-684000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-714900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-697400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-623500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-524800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-488400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-464000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-439000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-394500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-394900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-370600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-407400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-394500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-400400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-389900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-350800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-341100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-342600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-336400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-328200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-315600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-313400</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>768500</v>
+      </c>
+      <c r="E76" s="3">
         <v>741800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>768200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>725900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>713000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>695400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>701700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>652100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>652600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>705200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>791300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>810500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>821400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>837900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>880800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>876800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>887700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>342400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>381600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>356100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>357500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>98200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>111900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>104100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>105600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>108500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>118000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>36400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>30900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-73900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-98700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-36400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-24400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-24300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>36800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-12900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-39100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,94 +6605,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E83" s="3">
         <v>6000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>64800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8600</v>
-      </c>
-      <c r="K83" s="3">
-        <v>7400</v>
       </c>
       <c r="L83" s="3">
         <v>7400</v>
       </c>
       <c r="M83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="N83" s="3">
         <v>77400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>46600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>46200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>49800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>48700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>35900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>14600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>7300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>9000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E89" s="3">
         <v>2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>114700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>91300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>89600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-60400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>89100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>82100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>74100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>88700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>39900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>42300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>68600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>30600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-16300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>22200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,94 +7261,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-35500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-636800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>51100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>5300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7449,8 +7683,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,262 +8004,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-39500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-62200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-30600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-33200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-51800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-10800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>332700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>355600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>10600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-800</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-53500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>96000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>60800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>73600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-73400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>44100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>29800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-89900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>72700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>28500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>42300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-275400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>350900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>37500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>10100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>MGNI</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>205400</v>
+      </c>
+      <c r="E8" s="3">
         <v>179500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>173300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>155800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>194000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>162000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>162900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>149300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>186900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>150100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>152500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>130200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>175400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>145800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>137800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>118100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>161300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>131900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>114500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>60700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>82000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>61000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>42300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>36300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>48500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>37600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>37900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>32400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>41400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E9" s="3">
         <v>69400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>65000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>62800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>67800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>62500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>62600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>65900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>70000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>84900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>130200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>124800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>111000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>71800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>65000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>59400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>66800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>63500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>50500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>21200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>21000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>21500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13900</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>15100</v>
       </c>
       <c r="AD9" s="3">
         <v>15100</v>
       </c>
       <c r="AE9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="AF9" s="3">
         <v>15500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E10" s="3">
         <v>110100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>108400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>93000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>126200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>99500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>83400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>116900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>65200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>22400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>64400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>74000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>72800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>58700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>94500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>68400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>64000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>39900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>60800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>40000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>20800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>35200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>22800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>17300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>25900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1110,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E12" s="3">
         <v>20200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21600</v>
-      </c>
-      <c r="F12" s="3">
-        <v>22300</v>
       </c>
       <c r="G12" s="3">
         <v>22300</v>
       </c>
       <c r="H12" s="3">
+        <v>22300</v>
+      </c>
+      <c r="I12" s="3">
         <v>20300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24900</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>22800</v>
       </c>
       <c r="R12" s="3">
         <v>22800</v>
       </c>
       <c r="S12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="T12" s="3">
         <v>20800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>17900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>14200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>14100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>8600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,83 +1298,86 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3">
         <v>2200</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-8300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-5400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1100</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>32000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>11300</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1374,100 +1393,106 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="3">
         <v>12300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>15600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>39300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>88900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>95800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>15400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>19200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>19300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>19500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>23800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>23900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4700</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>500</v>
       </c>
       <c r="AA15" s="3">
         <v>500</v>
       </c>
       <c r="AB15" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC15" s="3">
         <v>300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>600</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>500</v>
       </c>
       <c r="AF15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>153200</v>
+      </c>
+      <c r="E17" s="3">
         <v>154500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>151400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>157100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>153800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>146900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>153300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>163100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>151800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>167900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>224300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>223200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>203900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>167000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>161000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>157900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>157700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>155800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>161500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>74500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>74000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>71900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>82900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>47000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>47500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>44300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>46500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>45700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>43900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E18" s="3">
         <v>25000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>22000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>40200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>35100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-71800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-93000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-28500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-23200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-39800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-23900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-47000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-40600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,231 +1747,238 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E21" s="3">
         <v>37900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>29400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>51900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>35400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>38300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>21800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>47400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>19700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-15000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>19100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-24300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1900</v>
       </c>
-      <c r="AC21" s="3">
-        <v>0</v>
-      </c>
       <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4700</v>
+        <v>7500</v>
       </c>
       <c r="E22" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F22" s="3">
         <v>5100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5200</v>
       </c>
-      <c r="G22" s="3">
-        <v>5400</v>
-      </c>
       <c r="H22" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J22" s="3">
         <v>6800</v>
       </c>
-      <c r="I22" s="3">
-        <v>6800</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8200</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1991,192 +2030,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E23" s="3">
         <v>20900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>42300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>33200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-73200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-99000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-39100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-25100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-46600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-29000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-50900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-38800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-87700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>200</v>
       </c>
       <c r="W24" s="3">
         <v>200</v>
       </c>
       <c r="X24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-900</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>100</v>
       </c>
       <c r="AC24" s="3">
         <v>100</v>
       </c>
       <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-700</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>100</v>
       </c>
       <c r="AF24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E26" s="3">
         <v>20100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>36400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-73900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-98700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-36400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-25000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-44600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-24300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>36800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-39100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E27" s="3">
         <v>20100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>36400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-73900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-98700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-36400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-25000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-44600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-24300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>36800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-39100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2623,20 +2683,23 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E33" s="3">
         <v>20100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>36400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-73900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-98700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-36400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-25000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-44600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-24300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>36800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-39100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E35" s="3">
         <v>20100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>36400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-73900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-98700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-36400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-25000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-44600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-24300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>36800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-39100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>553400</v>
+      </c>
+      <c r="E41" s="3">
         <v>482100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>426000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>429700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>483200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>387200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>326500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>252800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>326200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>310500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>266400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>236600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>326300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>253600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>233100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>204600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>230400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>188200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>193000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>468600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>117700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>103800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>107500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>71300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>88900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>85100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>86100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>80700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>80500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>82400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3531,105 +3620,111 @@
         <v>0</v>
       </c>
       <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
         <v>7500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1302000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1215400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1303000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1053200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1200000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1163800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1122400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>999800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1176300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>937200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>908400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>875300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>976500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>804400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>886100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>783000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>927800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>765100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>780500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>401800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>471700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>412400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>292400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>158200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>217600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>172300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>178000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>155900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>205700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>155300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3666,8 +3761,8 @@
       <c r="N44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3755,157 +3853,163 @@
       <c r="M45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>22600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>21000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>30600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>13400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1881600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1725500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1756500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1515100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1703200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1573400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1468200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1273500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1523000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1269200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1196900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1137000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1326300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1079300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1141800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1009800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1178100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>974300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1004000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>887800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>607100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>529600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>410200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>236900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>313100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>263200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>270000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>244100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>300500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>260900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3942,8 +4046,8 @@
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3996,192 +4100,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>175200</v>
+      </c>
+      <c r="E48" s="3">
         <v>162500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>147900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>134900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>119100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>122100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>125000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>119500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>107900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>110700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>115300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>116800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>123200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>119900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>112100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>107300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>111100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>97400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>83400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>66200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>63300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>61600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>63500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>45200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>47000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>38800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>41100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>33500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1025100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1027100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1016500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1018800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1026200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1033200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1039000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1044800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1051200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1058500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1088500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1168500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1255400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1323800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1361400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1398500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1416600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1455400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1447000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>256500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>264200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>272300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>280000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>34300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>34800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>23100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>23800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>24200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>24700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,82 +4480,85 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
         <v>5600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I52" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K52" s="3">
+        <v>16300</v>
+      </c>
+      <c r="L52" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="N52" s="3">
+        <v>7000</v>
+      </c>
+      <c r="O52" s="3">
+        <v>7200</v>
+      </c>
+      <c r="P52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Q52" s="3">
         <v>6100</v>
       </c>
-      <c r="H52" s="3">
-        <v>9100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>11000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>16300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>6300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>6700</v>
-      </c>
-      <c r="M52" s="3">
-        <v>7000</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>7200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>7400</v>
-      </c>
-      <c r="P52" s="3">
-        <v>6100</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>7200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>6900</v>
       </c>
       <c r="S52" s="3">
         <v>6900</v>
       </c>
       <c r="T52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="U52" s="3">
         <v>6100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1900</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>2100</v>
       </c>
       <c r="AB52" s="3">
         <v>2100</v>
@@ -4451,13 +4570,16 @@
         <v>2100</v>
       </c>
       <c r="AE52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3164400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2920700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2927100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2674700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2854800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2737900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2643200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2454100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2688800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2445000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2407800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2429900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2712200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2529100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2622500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2522500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2712600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2533100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2541300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1214700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>939000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>866500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>757100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>314200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>395100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>335300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>334800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>311400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>360000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,138 +4837,142 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1587100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1458000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1508200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1284200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1448700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1366500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1280000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1105600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1357100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1085700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1006600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>934800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1076900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>872700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>953500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>838700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>983100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>806500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>820100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>426700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>496900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>444400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>337700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>188800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>252700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>200900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>207300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>182500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>233500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>228600</v>
+      </c>
+      <c r="E58" s="3">
         <v>228400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>227300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>223800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>23700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>23600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>25100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24500</v>
-      </c>
-      <c r="O58" s="3">
-        <v>3600</v>
       </c>
       <c r="P58" s="3">
         <v>3600</v>
@@ -4859,8 +4992,8 @@
       <c r="U58" s="3">
         <v>3600</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>10</v>
+      <c r="V58" s="3">
+        <v>3600</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>10</v>
@@ -4877,8 +5010,8 @@
       <c r="AA58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -4892,255 +5025,264 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E59" s="3">
         <v>5900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>44500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>45100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>45000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>42700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>48800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>50000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>25300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>29200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>24700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1841700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1713000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1765000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1538500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1496000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1413600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1329100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1154700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1402100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1131100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1054000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>982400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1125000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>919000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1002200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>887300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1029400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>858900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>873700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>449000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>522200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>473600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>362300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>202100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>267500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>214500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>220500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>195500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>241000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>202200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>397800</v>
+      </c>
+      <c r="E61" s="3">
         <v>396900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>392000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>392800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>589100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>596700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>599300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>602100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>582700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>655600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>693900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>735600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>722800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>722100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>721400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>720700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>720000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>719300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>718600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>388600</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -5168,100 +5310,106 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1700</v>
       </c>
-      <c r="G62" s="3">
-        <v>800</v>
-      </c>
       <c r="H62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I62" s="3">
         <v>1600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1600</v>
       </c>
       <c r="K62" s="3">
         <v>1600</v>
       </c>
       <c r="L62" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="M62" s="3">
         <v>1800</v>
       </c>
       <c r="N62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O62" s="3">
         <v>2000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>73100</v>
-      </c>
-      <c r="P62" s="3">
-        <v>77500</v>
       </c>
       <c r="Q62" s="3">
         <v>77500</v>
       </c>
       <c r="R62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="S62" s="3">
         <v>76500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>82400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>78100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>61300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>34800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>35100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>36700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>37300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>15700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2242000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2112700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2158700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1932900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2086600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2012000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1930200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1758700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1987100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1792900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1755200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1724600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1920900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1718600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1801100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1684600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1831900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1656300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1653600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>872400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>557300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>510300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>399700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>216000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>283200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>231200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>229200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>202900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>242000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-516600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-639600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-659700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-670800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-661200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-697600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-702800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-701700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-684000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-714900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-697400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-623500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-524800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-488400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-464000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-439000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-394500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-394900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-370600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-407400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-394500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-400400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-389900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-350800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-341100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-342600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-336400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-328200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-315600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-313400</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>922400</v>
+      </c>
+      <c r="E76" s="3">
         <v>808000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>768500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>741800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>768200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>725900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>713000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>695400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>701700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>652100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>652600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>705200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>791300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>810500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>821400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>837900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>880800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>876800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>887700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>342400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>381600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>356100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>357500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>98200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>111900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>104100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>105600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>108500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>118000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E81" s="3">
         <v>20100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>36400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-73900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-98700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-36400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-25000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-44600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-24300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>36800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-39100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E83" s="3">
         <v>7000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>64800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8600</v>
-      </c>
-      <c r="M83" s="3">
-        <v>7400</v>
       </c>
       <c r="N83" s="3">
         <v>7400</v>
       </c>
       <c r="O83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="P83" s="3">
         <v>77400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>46600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>46200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>45900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>49800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>48700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>35900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>14100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>14600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>7500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E89" s="3">
         <v>86600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>114700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>91300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>89600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-60400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>89100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>82100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>74100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>88700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>39900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>42300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>68600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>30600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>12000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>22200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-31300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-636800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>51100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>5300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7923,8 +8156,8 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-39500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-62200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-30600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-33200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-51800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>332700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>355600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>10600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-800</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E102" s="3">
         <v>56100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-53500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>96000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>60800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>73600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-73400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>44100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>29800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-89900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>72700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>28500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-25800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>42300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-275400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>350900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>12600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>37500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>10100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGNI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>MGNI</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>164400</v>
+      </c>
+      <c r="E8" s="3">
         <v>205400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>179500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>173300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>155800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>194000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>162000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>162900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>149300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>186900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>150100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>152500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>130200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>175400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>145800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>137800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>118100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>161300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>131900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>114500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>60700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>82000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>61000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>42300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>36300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>48500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>37600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>37900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>32400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>41400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E9" s="3">
         <v>69500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>69400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>65000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>62800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>67800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>62500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>62600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>65900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>70000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>84900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>130200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>124800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>111000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>71800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>65000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>59400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>66800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>63500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>50500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>21200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>21000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>21500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>14000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13900</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>15100</v>
       </c>
       <c r="AE9" s="3">
         <v>15100</v>
       </c>
       <c r="AF9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="AG9" s="3">
         <v>15500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E10" s="3">
         <v>135800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>110100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>108400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>93000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>126200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>99500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>83400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>116900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>65200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>64400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>74000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>72800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>58700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>94500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>68400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>64000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>39900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>60800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>40000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>20800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>35200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>23700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>22800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>17300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>25900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E12" s="3">
         <v>20600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>22300</v>
       </c>
       <c r="H12" s="3">
         <v>22300</v>
       </c>
       <c r="I12" s="3">
+        <v>22300</v>
+      </c>
+      <c r="J12" s="3">
         <v>20300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>22300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24900</v>
-      </c>
-      <c r="R12" s="3">
-        <v>22800</v>
       </c>
       <c r="S12" s="3">
         <v>22800</v>
       </c>
       <c r="T12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="U12" s="3">
         <v>20800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>20900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>17900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>14200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>14100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>13000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>10200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,86 +1318,89 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3">
         <v>2200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-8300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-5400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1100</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>32000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>11300</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1396,103 +1416,109 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E15" s="3">
         <v>10000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>15600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>13600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>39300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>88900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>95800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>15400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>19200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>19300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>19500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>23800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>23900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>16800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4700</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>500</v>
       </c>
       <c r="AB15" s="3">
         <v>500</v>
       </c>
       <c r="AC15" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD15" s="3">
         <v>300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>600</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>500</v>
       </c>
       <c r="AG15" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>156700</v>
+      </c>
+      <c r="E17" s="3">
         <v>153200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>154500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>151400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>157100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>153800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>146900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>153300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>163100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>151800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>167900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>224300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>223200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>203900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>167000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>161000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>157900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>157700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>155800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>161500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>74500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>74000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>71900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>82900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>47000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>47500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>44300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>46500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>45700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>43900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E18" s="3">
         <v>52100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>25000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>22000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>40200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-17800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-71800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-93000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-23200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-39800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-23900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-47000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-40600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-8600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-13300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,240 +1781,247 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E21" s="3">
         <v>62200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>37900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>29400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>51900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>35400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>38300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>21100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>47400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>19700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-15000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>19100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1900</v>
       </c>
-      <c r="AD21" s="3">
-        <v>0</v>
-      </c>
       <c r="AE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E22" s="3">
         <v>7500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8200</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -2033,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>48100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>20900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>42300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-73200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-99000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-39100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-25100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-46600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-29000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-50900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-12700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-38800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-13300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-75000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-87700</v>
-      </c>
-      <c r="W24" s="3">
-        <v>200</v>
       </c>
       <c r="X24" s="3">
         <v>200</v>
       </c>
       <c r="Y24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-900</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>100</v>
       </c>
       <c r="AD24" s="3">
         <v>100</v>
       </c>
       <c r="AE24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-700</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>100</v>
       </c>
       <c r="AG24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E26" s="3">
         <v>123100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>36400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-73900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-98700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-36400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-25000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-44600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-24300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>36800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-12900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E27" s="3">
         <v>123100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>36400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>30900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-73900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-98700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-36400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-25000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-44600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-24300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>36800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2686,20 +2747,23 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>10</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E33" s="3">
         <v>123100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>36400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-73900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-98700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-36400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-25000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-44600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-24300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>36800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E35" s="3">
         <v>123100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>36400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>30900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-73900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-98700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-36400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-25000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-44600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-24300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>36800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>184600</v>
+      </c>
+      <c r="E41" s="3">
         <v>553400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>482100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>426000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>429700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>483200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>387200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>326500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>252800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>326200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>310500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>266400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>236600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>326300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>253600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>233100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>204600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>230400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>188200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>193000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>468600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>117700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>103800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>107500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>71300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>88900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>85100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>86100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>80700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>80500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>82400</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3623,108 +3713,114 @@
         <v>0</v>
       </c>
       <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
         <v>7500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1430700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1302000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1215400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1303000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1053200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1200000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1163800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1122400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>999800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1176300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>937200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>908400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>875300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>976500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>804400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>886100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>783000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>927800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>765100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>780500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>401800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>471700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>412400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>292400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>158200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>217600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>172300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>178000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>155900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>205700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>155300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3764,8 +3860,8 @@
       <c r="O44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3856,160 +3955,166 @@
       <c r="N45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>21400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>21000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>30600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>17700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>13400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1647600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1881600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1725500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1756500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1515100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1703200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1573400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1468200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1273500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1523000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1269200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1196900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1137000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1326300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1079300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1141800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1009800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1178100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>974300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1004000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>887800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>607100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>529600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>410200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>236900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>313100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>263200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>270000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>244100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>300500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>260900</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4049,8 +4154,8 @@
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4103,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>190500</v>
+      </c>
+      <c r="E48" s="3">
         <v>175200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>162500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>147900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>134900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>119100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>122100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>125000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>119500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>107900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>110700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>115300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>116800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>123200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>119900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>112100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>107300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>111100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>97400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>83400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>66200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>63300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>61600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>63500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>41100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>45200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>47000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>38800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>41100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>33500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1023100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1025100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1027100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1016500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1018800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1026200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1033200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1039000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1044800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1051200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1058500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1088500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1168500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1255400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1323800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1361400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1398500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1416600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1455400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1447000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>256500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>264200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>272300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>280000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>34300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>34800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>23100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>23800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>24200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>24700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,85 +4600,88 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>85300</v>
+      </c>
+      <c r="E52" s="3">
         <v>6200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7200</v>
-      </c>
-      <c r="S52" s="3">
-        <v>6900</v>
       </c>
       <c r="T52" s="3">
         <v>6900</v>
       </c>
       <c r="U52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="V52" s="3">
         <v>6100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1900</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>2100</v>
       </c>
       <c r="AC52" s="3">
         <v>2100</v>
@@ -4573,13 +4693,16 @@
         <v>2100</v>
       </c>
       <c r="AF52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AG52" s="3">
         <v>1200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2946500</v>
+      </c>
+      <c r="E54" s="3">
         <v>3164400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2920700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2927100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2674700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2854800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2737900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2643200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2454100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2688800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2445000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2407800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2429900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2712200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2529100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2622500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2522500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2712600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2533100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2541300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1214700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>939000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>866500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>757100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>314200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>395100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>335300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>334800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>311400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>360000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,144 +4968,148 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1565700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1587100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1458000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1508200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1284200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1448700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1366500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1280000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1105600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1357100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1085700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1006600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>934800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1076900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>872700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>953500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>838700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>983100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>806500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>820100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>426700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>496900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>444400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>337700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>188800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>252700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>200900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>207300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>182500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>233500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E58" s="3">
         <v>228600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>228400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>227300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>223800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>23700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>23600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>25100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>24500</v>
-      </c>
-      <c r="P58" s="3">
-        <v>3600</v>
       </c>
       <c r="Q58" s="3">
         <v>3600</v>
@@ -4995,8 +5129,8 @@
       <c r="V58" s="3">
         <v>3600</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>10</v>
+      <c r="W58" s="3">
+        <v>3600</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>10</v>
@@ -5013,8 +5147,8 @@
       <c r="AB58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5028,264 +5162,273 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>44500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>45100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>45000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>42700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>50000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>25300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>29200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>24700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1620900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1841700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1713000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1765000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1538500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1496000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1413600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1329100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1154700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1402100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1131100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1054000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>982400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1125000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>919000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1002200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>887300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1029400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>858900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>873700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>449000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>522200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>473600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>362300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>202100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>267500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>214500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>220500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>195500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>241000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>202200</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>404300</v>
+      </c>
+      <c r="E61" s="3">
         <v>397800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>396900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>392000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>392800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>589100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>596700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>599300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>602100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>582700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>655600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>693900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>735600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>722800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>722100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>721400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>720700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>720000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>719300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>718600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>388600</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5313,103 +5456,109 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1500</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1600</v>
       </c>
       <c r="L62" s="3">
         <v>1600</v>
       </c>
       <c r="M62" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="N62" s="3">
         <v>1800</v>
       </c>
       <c r="O62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P62" s="3">
         <v>2000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>73100</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>77500</v>
       </c>
       <c r="R62" s="3">
         <v>77500</v>
       </c>
       <c r="S62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="T62" s="3">
         <v>76500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>82400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>78100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>61300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>34800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>35100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>36700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>15700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2028600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2242000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2112700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2158700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1932900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2086600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2012000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1930200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1758700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1987100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1792900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1755200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1724600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1920900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1718600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1801100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1684600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1831900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1656300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1653600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>872400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>557300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>510300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>399700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>216000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>283200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>231200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>229200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>202900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>242000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-512100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-516600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-639600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-659700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-670800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-661200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-697600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-702800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-701700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-684000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-714900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-697400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-623500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-524800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-488400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-464000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-439000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-394500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-394900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-370600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-407400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-394500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-400400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-389900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-350800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-341100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-342600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-336400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-328200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-315600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-313400</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>917900</v>
+      </c>
+      <c r="E76" s="3">
         <v>922400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>808000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>768500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>741800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>768200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>725900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>713000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>695400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>701700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>652100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>652600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>705200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>791300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>810500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>821400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>837900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>880800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>876800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>887700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>342400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>381600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>356100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>357500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>98200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>111900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>104100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>105600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>108500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>118000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E81" s="3">
         <v>123100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>36400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>30900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-73900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-98700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-36400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-25000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-44600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-24300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>36800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-13800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E83" s="3">
         <v>4200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>64800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8600</v>
-      </c>
-      <c r="N83" s="3">
-        <v>7400</v>
       </c>
       <c r="O83" s="3">
         <v>7400</v>
       </c>
       <c r="P83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Q83" s="3">
         <v>77400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>46600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>46200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>45900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>49800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>48700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>35900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>14100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>14600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>7300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>9000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-120800</v>
+      </c>
+      <c r="E89" s="3">
         <v>128500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>86600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>114700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>91300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>89600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-60400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>89100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>82100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>74100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>88700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>39900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>42300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>68600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>30600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>28600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>12000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-16300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>22200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-31300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-636800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>51100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>5300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8159,8 +8393,8 @@
       <c r="O96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-235100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-28000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-39500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-62200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-30600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-33200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-51800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-16400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-10800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>332700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>355600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>10600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-800</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG101" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-368700</v>
+      </c>
+      <c r="E102" s="3">
         <v>71200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>56100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-53500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>96000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>60800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>73600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-73400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>44100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>29800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-89900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>72700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>20400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>28500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-25800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>42300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-275400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>350900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>37500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>10100</v>
       </c>
     </row>
